--- a/data/nzd0386/nzd0386.xlsx
+++ b/data/nzd0386/nzd0386.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K400"/>
+  <dimension ref="A1:K402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16044,6 +16044,84 @@
         <v>501.98</v>
       </c>
       <c r="K400" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>472</v>
+      </c>
+      <c r="C401" t="n">
+        <v>461.37</v>
+      </c>
+      <c r="D401" t="n">
+        <v>468.19</v>
+      </c>
+      <c r="E401" t="n">
+        <v>467.83</v>
+      </c>
+      <c r="F401" t="n">
+        <v>467.93</v>
+      </c>
+      <c r="G401" t="n">
+        <v>465.09</v>
+      </c>
+      <c r="H401" t="n">
+        <v>484.14</v>
+      </c>
+      <c r="I401" t="n">
+        <v>497.64</v>
+      </c>
+      <c r="J401" t="n">
+        <v>502.9</v>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>471.71</v>
+      </c>
+      <c r="C402" t="n">
+        <v>460.59</v>
+      </c>
+      <c r="D402" t="n">
+        <v>467.48</v>
+      </c>
+      <c r="E402" t="n">
+        <v>468.43</v>
+      </c>
+      <c r="F402" t="n">
+        <v>467.95</v>
+      </c>
+      <c r="G402" t="n">
+        <v>464.98</v>
+      </c>
+      <c r="H402" t="n">
+        <v>484.52</v>
+      </c>
+      <c r="I402" t="n">
+        <v>497.12</v>
+      </c>
+      <c r="J402" t="n">
+        <v>502.47</v>
+      </c>
+      <c r="K402" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16060,7 +16138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B408"/>
+  <dimension ref="A1:B410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20143,6 +20221,26 @@
       </c>
       <c r="B408" t="n">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>-0.54</v>
       </c>
     </row>
   </sheetData>
@@ -20311,28 +20409,28 @@
         <v>0.0545</v>
       </c>
       <c r="I2" t="n">
-        <v>6.305085159129247</v>
+        <v>6.304694892088663</v>
       </c>
       <c r="J2" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K2" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5576228893516393</v>
+        <v>0.5604425745657733</v>
       </c>
       <c r="M2" t="n">
-        <v>32.14217335275065</v>
+        <v>31.98466161818342</v>
       </c>
       <c r="N2" t="n">
-        <v>1856.354237906035</v>
+        <v>1847.096783729027</v>
       </c>
       <c r="O2" t="n">
-        <v>43.08542953140928</v>
+        <v>42.97786388047953</v>
       </c>
       <c r="P2" t="n">
-        <v>301.977154456066</v>
+        <v>301.9811637978684</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20389,28 +20487,28 @@
         <v>0.0595</v>
       </c>
       <c r="I3" t="n">
-        <v>6.189698200297308</v>
+        <v>6.183993521362406</v>
       </c>
       <c r="J3" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K3" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6646431334176501</v>
+        <v>0.6667730486275867</v>
       </c>
       <c r="M3" t="n">
-        <v>28.05045607619385</v>
+        <v>27.94766492424589</v>
       </c>
       <c r="N3" t="n">
-        <v>1137.848690361496</v>
+        <v>1132.340749889783</v>
       </c>
       <c r="O3" t="n">
-        <v>33.73201284183165</v>
+        <v>33.65027117111812</v>
       </c>
       <c r="P3" t="n">
-        <v>299.632548532321</v>
+        <v>299.6911208746363</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20467,28 +20565,28 @@
         <v>0.073</v>
       </c>
       <c r="I4" t="n">
-        <v>6.273773122705843</v>
+        <v>6.269951021637721</v>
       </c>
       <c r="J4" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K4" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6657824428411043</v>
+        <v>0.668065668156143</v>
       </c>
       <c r="M4" t="n">
-        <v>28.43316372730702</v>
+        <v>28.31676206999575</v>
       </c>
       <c r="N4" t="n">
-        <v>1163.004582640614</v>
+        <v>1157.279655133335</v>
       </c>
       <c r="O4" t="n">
-        <v>34.10285299854858</v>
+        <v>34.01881325286547</v>
       </c>
       <c r="P4" t="n">
-        <v>302.2967706834531</v>
+        <v>302.3360151137124</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20545,28 +20643,28 @@
         <v>0.1158</v>
       </c>
       <c r="I5" t="n">
-        <v>6.483539037216149</v>
+        <v>6.479308372048027</v>
       </c>
       <c r="J5" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K5" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6716932012764285</v>
+        <v>0.673934455675038</v>
       </c>
       <c r="M5" t="n">
-        <v>29.18079866637747</v>
+        <v>29.06521706539247</v>
       </c>
       <c r="N5" t="n">
-        <v>1209.372444780874</v>
+        <v>1203.431985201463</v>
       </c>
       <c r="O5" t="n">
-        <v>34.77603261990755</v>
+        <v>34.69051722303175</v>
       </c>
       <c r="P5" t="n">
-        <v>297.3502819949534</v>
+        <v>297.3937148803128</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20623,28 +20721,28 @@
         <v>0.0964</v>
       </c>
       <c r="I6" t="n">
-        <v>6.282284960299885</v>
+        <v>6.278350025761267</v>
       </c>
       <c r="J6" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K6" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6884937957787984</v>
+        <v>0.6906844491954401</v>
       </c>
       <c r="M6" t="n">
-        <v>27.08797802333262</v>
+        <v>26.9805618488651</v>
       </c>
       <c r="N6" t="n">
-        <v>1051.063170378101</v>
+        <v>1045.899915069793</v>
       </c>
       <c r="O6" t="n">
-        <v>32.42010441652064</v>
+        <v>32.34037592653791</v>
       </c>
       <c r="P6" t="n">
-        <v>302.2852766690432</v>
+        <v>302.3256761016382</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20701,28 +20799,28 @@
         <v>0.1215</v>
       </c>
       <c r="I7" t="n">
-        <v>6.29305265979939</v>
+        <v>6.287073652703384</v>
       </c>
       <c r="J7" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K7" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6814107126401265</v>
+        <v>0.6834680940210904</v>
       </c>
       <c r="M7" t="n">
-        <v>27.37941208387504</v>
+        <v>27.28448383303961</v>
       </c>
       <c r="N7" t="n">
-        <v>1089.862798061131</v>
+        <v>1084.609354172628</v>
       </c>
       <c r="O7" t="n">
-        <v>33.01307010959646</v>
+        <v>32.93340787365662</v>
       </c>
       <c r="P7" t="n">
-        <v>301.1763269595497</v>
+        <v>301.2377125564593</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -20779,28 +20877,28 @@
         <v>0.0993</v>
       </c>
       <c r="I8" t="n">
-        <v>7.119499093377191</v>
+        <v>7.11556381295714</v>
       </c>
       <c r="J8" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K8" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6850422022694783</v>
+        <v>0.6872815630893296</v>
       </c>
       <c r="M8" t="n">
-        <v>31.29180626590397</v>
+        <v>31.16391793939798</v>
       </c>
       <c r="N8" t="n">
-        <v>1371.705250801159</v>
+        <v>1364.942732567489</v>
       </c>
       <c r="O8" t="n">
-        <v>37.036539400991</v>
+        <v>36.94513137840342</v>
       </c>
       <c r="P8" t="n">
-        <v>296.0717553461802</v>
+        <v>296.1121568271558</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -20857,28 +20955,28 @@
         <v>0.0742</v>
       </c>
       <c r="I9" t="n">
-        <v>7.665324695366641</v>
+        <v>7.662061363700749</v>
       </c>
       <c r="J9" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K9" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6878928312442201</v>
+        <v>0.6901802537582901</v>
       </c>
       <c r="M9" t="n">
-        <v>33.59657552336561</v>
+        <v>33.45211254097006</v>
       </c>
       <c r="N9" t="n">
-        <v>1569.173471345775</v>
+        <v>1561.402310691524</v>
       </c>
       <c r="O9" t="n">
-        <v>39.6127942885348</v>
+        <v>39.51458351914549</v>
       </c>
       <c r="P9" t="n">
-        <v>293.6959124020194</v>
+        <v>293.7294195967171</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -20935,28 +21033,28 @@
         <v>0.0835</v>
       </c>
       <c r="I10" t="n">
-        <v>7.70672135796045</v>
+        <v>7.703864339897585</v>
       </c>
       <c r="J10" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K10" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6932541734139964</v>
+        <v>0.6955446624959531</v>
       </c>
       <c r="M10" t="n">
-        <v>33.24114964592368</v>
+        <v>33.09600235438312</v>
       </c>
       <c r="N10" t="n">
-        <v>1546.864843498044</v>
+        <v>1539.192097921367</v>
       </c>
       <c r="O10" t="n">
-        <v>39.33020268824004</v>
+        <v>39.23253876467042</v>
       </c>
       <c r="P10" t="n">
-        <v>297.4688576518195</v>
+        <v>297.4981929713591</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -20994,7 +21092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K400"/>
+  <dimension ref="A1:K402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43797,6 +43895,120 @@
         </is>
       </c>
     </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>-42.21793452953128,173.86441788609554</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>-42.21799016951446,173.86351262492207</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>-42.21816296159861,173.86281475844052</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>-42.21839223018223,173.86218412007452</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>-42.21866809686944,173.86148153199736</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>-42.218988630586,173.86078126445497</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>-42.219496003286544,173.86018054331862</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>-42.21992647255279,173.85963239632065</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>-42.22034944026403,173.85908326875875</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>-42.217931988196675,173.86441707618707</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>-42.217983334188176,173.86351044661197</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>-42.21815694734219,173.86281183783427</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>-42.21839702552422,173.86218747040746</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>-42.21866825045809,173.86148165857117</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>-42.2189878140089,173.86078050992836</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>-42.21949880570986,173.86018318571755</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>-42.219922816999784,173.85962845850523</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>-42.22034655474423,173.8590797942579</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0386/nzd0386.xlsx
+++ b/data/nzd0386/nzd0386.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K402"/>
+  <dimension ref="A1:K404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16122,6 +16122,84 @@
         <v>502.47</v>
       </c>
       <c r="K402" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>473.43</v>
+      </c>
+      <c r="C403" t="n">
+        <v>461.98</v>
+      </c>
+      <c r="D403" t="n">
+        <v>467.79</v>
+      </c>
+      <c r="E403" t="n">
+        <v>468.82</v>
+      </c>
+      <c r="F403" t="n">
+        <v>468.3</v>
+      </c>
+      <c r="G403" t="n">
+        <v>465.13</v>
+      </c>
+      <c r="H403" t="n">
+        <v>484.65</v>
+      </c>
+      <c r="I403" t="n">
+        <v>497.38</v>
+      </c>
+      <c r="J403" t="n">
+        <v>502.87</v>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:07+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>473.09</v>
+      </c>
+      <c r="C404" t="n">
+        <v>461.5</v>
+      </c>
+      <c r="D404" t="n">
+        <v>467.31</v>
+      </c>
+      <c r="E404" t="n">
+        <v>468.54</v>
+      </c>
+      <c r="F404" t="n">
+        <v>468.02</v>
+      </c>
+      <c r="G404" t="n">
+        <v>464.9</v>
+      </c>
+      <c r="H404" t="n">
+        <v>484.34</v>
+      </c>
+      <c r="I404" t="n">
+        <v>497.46</v>
+      </c>
+      <c r="J404" t="n">
+        <v>503.04</v>
+      </c>
+      <c r="K404" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16138,7 +16216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B410"/>
+  <dimension ref="A1:B412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20241,6 +20319,26 @@
       </c>
       <c r="B410" t="n">
         <v>-0.54</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>-0.36</v>
       </c>
     </row>
   </sheetData>
@@ -20409,28 +20507,28 @@
         <v>0.0545</v>
       </c>
       <c r="I2" t="n">
-        <v>6.304694892088663</v>
+        <v>6.305206487744177</v>
       </c>
       <c r="J2" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K2" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5604425745657733</v>
+        <v>0.563304893997517</v>
       </c>
       <c r="M2" t="n">
-        <v>31.98466161818342</v>
+        <v>31.82744085840059</v>
       </c>
       <c r="N2" t="n">
-        <v>1847.096783729027</v>
+        <v>1837.932120107155</v>
       </c>
       <c r="O2" t="n">
-        <v>42.97786388047953</v>
+        <v>42.87111055369519</v>
       </c>
       <c r="P2" t="n">
-        <v>301.9811637978684</v>
+        <v>301.9758997682186</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20487,28 +20585,28 @@
         <v>0.0595</v>
       </c>
       <c r="I3" t="n">
-        <v>6.183993521362406</v>
+        <v>6.178718580589481</v>
       </c>
       <c r="J3" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K3" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6667730486275867</v>
+        <v>0.6689094763623902</v>
       </c>
       <c r="M3" t="n">
-        <v>27.94766492424589</v>
+        <v>27.84289993237733</v>
       </c>
       <c r="N3" t="n">
-        <v>1132.340749889783</v>
+        <v>1126.865990698859</v>
       </c>
       <c r="O3" t="n">
-        <v>33.65027117111812</v>
+        <v>33.56882468450242</v>
       </c>
       <c r="P3" t="n">
-        <v>299.6911208746363</v>
+        <v>299.7454577207329</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20565,28 +20663,28 @@
         <v>0.073</v>
       </c>
       <c r="I4" t="n">
-        <v>6.269951021637721</v>
+        <v>6.265489010655029</v>
       </c>
       <c r="J4" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K4" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L4" t="n">
-        <v>0.668065668156143</v>
+        <v>0.6702689014372614</v>
       </c>
       <c r="M4" t="n">
-        <v>28.31676206999575</v>
+        <v>28.20556761815369</v>
       </c>
       <c r="N4" t="n">
-        <v>1157.279655133335</v>
+        <v>1151.640222011878</v>
       </c>
       <c r="O4" t="n">
-        <v>34.01881325286547</v>
+        <v>33.93582505276508</v>
       </c>
       <c r="P4" t="n">
-        <v>302.3360151137124</v>
+        <v>302.3819790201165</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20643,28 +20741,28 @@
         <v>0.1158</v>
       </c>
       <c r="I5" t="n">
-        <v>6.479308372048027</v>
+        <v>6.47523460609372</v>
       </c>
       <c r="J5" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K5" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L5" t="n">
-        <v>0.673934455675038</v>
+        <v>0.6761579148796264</v>
       </c>
       <c r="M5" t="n">
-        <v>29.06521706539247</v>
+        <v>28.9494986412763</v>
       </c>
       <c r="N5" t="n">
-        <v>1203.431985201463</v>
+        <v>1197.546006664226</v>
       </c>
       <c r="O5" t="n">
-        <v>34.69051722303175</v>
+        <v>34.60557768141179</v>
       </c>
       <c r="P5" t="n">
-        <v>297.3937148803128</v>
+        <v>297.4356786119594</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20721,28 +20819,28 @@
         <v>0.0964</v>
       </c>
       <c r="I6" t="n">
-        <v>6.278350025761267</v>
+        <v>6.274268431958741</v>
       </c>
       <c r="J6" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K6" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6906844491954401</v>
+        <v>0.6928342697127485</v>
       </c>
       <c r="M6" t="n">
-        <v>26.9805618488651</v>
+        <v>26.87506121425338</v>
       </c>
       <c r="N6" t="n">
-        <v>1045.899915069793</v>
+        <v>1040.796036944125</v>
       </c>
       <c r="O6" t="n">
-        <v>32.34037592653791</v>
+        <v>32.26137066127422</v>
       </c>
       <c r="P6" t="n">
-        <v>302.3256761016382</v>
+        <v>302.3677203470327</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20799,28 +20897,28 @@
         <v>0.1215</v>
       </c>
       <c r="I7" t="n">
-        <v>6.287073652703384</v>
+        <v>6.280765397247548</v>
       </c>
       <c r="J7" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K7" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6834680940210904</v>
+        <v>0.6854695781485762</v>
       </c>
       <c r="M7" t="n">
-        <v>27.28448383303961</v>
+        <v>27.19251665723091</v>
       </c>
       <c r="N7" t="n">
-        <v>1084.609354172628</v>
+        <v>1079.432911473461</v>
       </c>
       <c r="O7" t="n">
-        <v>32.93340787365662</v>
+        <v>32.85472434024459</v>
       </c>
       <c r="P7" t="n">
-        <v>301.2377125564593</v>
+        <v>301.3026905818871</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -20877,28 +20975,28 @@
         <v>0.0993</v>
       </c>
       <c r="I8" t="n">
-        <v>7.11556381295714</v>
+        <v>7.111359373702783</v>
       </c>
       <c r="J8" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K8" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6872815630893296</v>
+        <v>0.689473089377471</v>
       </c>
       <c r="M8" t="n">
-        <v>31.16391793939798</v>
+        <v>31.03903788777885</v>
       </c>
       <c r="N8" t="n">
-        <v>1364.942732567489</v>
+        <v>1358.260950181389</v>
       </c>
       <c r="O8" t="n">
-        <v>36.94513137840342</v>
+        <v>36.85459198229427</v>
       </c>
       <c r="P8" t="n">
-        <v>296.1121568271558</v>
+        <v>296.1554670339423</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -20955,28 +21053,28 @@
         <v>0.0742</v>
       </c>
       <c r="I9" t="n">
-        <v>7.662061363700749</v>
+        <v>7.658351143782518</v>
       </c>
       <c r="J9" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K9" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6901802537582901</v>
+        <v>0.6924106737828073</v>
       </c>
       <c r="M9" t="n">
-        <v>33.45211254097006</v>
+        <v>33.31208220721031</v>
       </c>
       <c r="N9" t="n">
-        <v>1561.402310691524</v>
+        <v>1553.724797261897</v>
       </c>
       <c r="O9" t="n">
-        <v>39.51458351914549</v>
+        <v>39.4173159571006</v>
       </c>
       <c r="P9" t="n">
-        <v>293.7294195967171</v>
+        <v>293.7676369220881</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21033,28 +21131,28 @@
         <v>0.0835</v>
       </c>
       <c r="I10" t="n">
-        <v>7.703864339897585</v>
+        <v>7.700769216458794</v>
       </c>
       <c r="J10" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K10" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6955446624959531</v>
+        <v>0.6977910248074249</v>
       </c>
       <c r="M10" t="n">
-        <v>33.09600235438312</v>
+        <v>32.9538820138243</v>
       </c>
       <c r="N10" t="n">
-        <v>1539.192097921367</v>
+        <v>1531.603094876764</v>
       </c>
       <c r="O10" t="n">
-        <v>39.23253876467042</v>
+        <v>39.135701027026</v>
       </c>
       <c r="P10" t="n">
-        <v>297.4981929713591</v>
+        <v>297.5300743924865</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21092,7 +21190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K402"/>
+  <dimension ref="A1:K404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44009,6 +44107,120 @@
         </is>
       </c>
     </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>-42.217947060939686,173.86442187978307</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>-42.21799551509011,173.86351432847263</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>-42.21815957328515,173.8628131130285</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>-42.21840014249646,173.86218964812417</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>-42.218670938259415,173.86148387361285</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>-42.21898892752312,173.8607815388283</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>-42.21949976443361,173.8601840896962</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>-42.21992464477631,173.85963042741287</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>-42.22034923894868,173.85908302635173</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:07+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>-42.217944081443996,173.86442093023484</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>-42.2179913087355,173.86351298797382</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>-42.21815550730894,173.86281113853428</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>-42.21839790467025,173.86218808463525</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>-42.21866878801836,173.8614821015795</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>-42.218987220134636,173.86077996118178</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>-42.21949747824619,173.86018193405488</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>-42.219925207169084,173.85963103323064</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>-42.22035037973556,173.8590843999917</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0386/nzd0386.xlsx
+++ b/data/nzd0386/nzd0386.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K404"/>
+  <dimension ref="A1:K405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16200,6 +16200,45 @@
         <v>503.04</v>
       </c>
       <c r="K404" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>473.49</v>
+      </c>
+      <c r="C405" t="n">
+        <v>461.7</v>
+      </c>
+      <c r="D405" t="n">
+        <v>467.29</v>
+      </c>
+      <c r="E405" t="n">
+        <v>468.6</v>
+      </c>
+      <c r="F405" t="n">
+        <v>467.93</v>
+      </c>
+      <c r="G405" t="n">
+        <v>464.22</v>
+      </c>
+      <c r="H405" t="n">
+        <v>484.17</v>
+      </c>
+      <c r="I405" t="n">
+        <v>497.81</v>
+      </c>
+      <c r="J405" t="n">
+        <v>503</v>
+      </c>
+      <c r="K405" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16216,7 +16255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B412"/>
+  <dimension ref="A1:B413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20339,6 +20378,16 @@
       </c>
       <c r="B412" t="n">
         <v>-0.36</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>
@@ -20507,28 +20556,28 @@
         <v>0.0545</v>
       </c>
       <c r="I2" t="n">
-        <v>6.305206487744177</v>
+        <v>6.305338661808859</v>
       </c>
       <c r="J2" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K2" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L2" t="n">
-        <v>0.563304893997517</v>
+        <v>0.5647207958720989</v>
       </c>
       <c r="M2" t="n">
-        <v>31.82744085840059</v>
+        <v>31.74904577582666</v>
       </c>
       <c r="N2" t="n">
-        <v>1837.932120107155</v>
+        <v>1833.382965502059</v>
       </c>
       <c r="O2" t="n">
-        <v>42.87111055369519</v>
+        <v>42.81802150382545</v>
       </c>
       <c r="P2" t="n">
-        <v>301.9758997682186</v>
+        <v>301.9745340026565</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20585,28 +20634,28 @@
         <v>0.0595</v>
       </c>
       <c r="I3" t="n">
-        <v>6.178718580589481</v>
+        <v>6.175879118684796</v>
       </c>
       <c r="J3" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K3" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6689094763623902</v>
+        <v>0.6699544175545356</v>
       </c>
       <c r="M3" t="n">
-        <v>27.84289993237733</v>
+        <v>27.7920932447772</v>
       </c>
       <c r="N3" t="n">
-        <v>1126.865990698859</v>
+        <v>1124.160863359761</v>
       </c>
       <c r="O3" t="n">
-        <v>33.56882468450242</v>
+        <v>33.52850821852594</v>
       </c>
       <c r="P3" t="n">
-        <v>299.7454577207329</v>
+        <v>299.7747981158686</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20663,28 +20712,28 @@
         <v>0.073</v>
       </c>
       <c r="I4" t="n">
-        <v>6.265489010655029</v>
+        <v>6.262940345254106</v>
       </c>
       <c r="J4" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K4" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6702689014372614</v>
+        <v>0.6713384565665567</v>
       </c>
       <c r="M4" t="n">
-        <v>28.20556761815369</v>
+        <v>28.15243605504269</v>
       </c>
       <c r="N4" t="n">
-        <v>1151.640222011878</v>
+        <v>1148.857419868689</v>
       </c>
       <c r="O4" t="n">
-        <v>33.93582505276508</v>
+        <v>33.89479930415121</v>
       </c>
       <c r="P4" t="n">
-        <v>302.3819790201165</v>
+        <v>302.4083145908837</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20741,28 +20790,28 @@
         <v>0.1158</v>
       </c>
       <c r="I5" t="n">
-        <v>6.47523460609372</v>
+        <v>6.472953883546212</v>
       </c>
       <c r="J5" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K5" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6761579148796264</v>
+        <v>0.6772443920738644</v>
       </c>
       <c r="M5" t="n">
-        <v>28.9494986412763</v>
+        <v>28.89368019315552</v>
       </c>
       <c r="N5" t="n">
-        <v>1197.546006664226</v>
+        <v>1194.636071482154</v>
       </c>
       <c r="O5" t="n">
-        <v>34.60557768141179</v>
+        <v>34.56350780060025</v>
       </c>
       <c r="P5" t="n">
-        <v>297.4356786119594</v>
+        <v>297.4592455070209</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20819,28 +20868,28 @@
         <v>0.0964</v>
       </c>
       <c r="I6" t="n">
-        <v>6.274268431958741</v>
+        <v>6.271920118438585</v>
       </c>
       <c r="J6" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K6" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6928342697127485</v>
+        <v>0.6938786331042228</v>
       </c>
       <c r="M6" t="n">
-        <v>26.87506121425338</v>
+        <v>26.8247408378424</v>
       </c>
       <c r="N6" t="n">
-        <v>1040.796036944125</v>
+        <v>1038.277362126504</v>
       </c>
       <c r="O6" t="n">
-        <v>32.26137066127422</v>
+        <v>32.22231155777784</v>
       </c>
       <c r="P6" t="n">
-        <v>302.3677203470327</v>
+        <v>302.391985665215</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20897,28 +20946,28 @@
         <v>0.1215</v>
       </c>
       <c r="I7" t="n">
-        <v>6.280765397247548</v>
+        <v>6.27704733773298</v>
       </c>
       <c r="J7" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K7" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6854695781485762</v>
+        <v>0.6864169915811482</v>
       </c>
       <c r="M7" t="n">
-        <v>27.19251665723091</v>
+        <v>27.15059879871527</v>
       </c>
       <c r="N7" t="n">
-        <v>1079.432911473461</v>
+        <v>1076.905321959239</v>
       </c>
       <c r="O7" t="n">
-        <v>32.85472434024459</v>
+        <v>32.81623564577813</v>
       </c>
       <c r="P7" t="n">
-        <v>301.3026905818871</v>
+        <v>301.3411095989254</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -20975,28 +21024,28 @@
         <v>0.0993</v>
       </c>
       <c r="I8" t="n">
-        <v>7.111359373702783</v>
+        <v>7.108871044127164</v>
       </c>
       <c r="J8" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K8" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L8" t="n">
-        <v>0.689473089377471</v>
+        <v>0.6905358485476445</v>
       </c>
       <c r="M8" t="n">
-        <v>31.03903788777885</v>
+        <v>30.97969172105405</v>
       </c>
       <c r="N8" t="n">
-        <v>1358.260950181389</v>
+        <v>1354.963538815867</v>
       </c>
       <c r="O8" t="n">
-        <v>36.85459198229427</v>
+        <v>36.80982937770653</v>
       </c>
       <c r="P8" t="n">
-        <v>296.1554670339423</v>
+        <v>296.1811791496273</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21053,28 +21102,28 @@
         <v>0.0742</v>
       </c>
       <c r="I9" t="n">
-        <v>7.658351143782518</v>
+        <v>7.65643277617856</v>
       </c>
       <c r="J9" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K9" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6924106737828073</v>
+        <v>0.693514995693129</v>
       </c>
       <c r="M9" t="n">
-        <v>33.31208220721031</v>
+        <v>33.24295259244436</v>
       </c>
       <c r="N9" t="n">
-        <v>1553.724797261897</v>
+        <v>1549.917351604731</v>
       </c>
       <c r="O9" t="n">
-        <v>39.4173159571006</v>
+        <v>39.36898972039708</v>
       </c>
       <c r="P9" t="n">
-        <v>293.7676369220881</v>
+        <v>293.7874595734936</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21131,28 +21180,28 @@
         <v>0.0835</v>
       </c>
       <c r="I10" t="n">
-        <v>7.700769216458794</v>
+        <v>7.698985686770515</v>
       </c>
       <c r="J10" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K10" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6977910248074249</v>
+        <v>0.6988930248684672</v>
       </c>
       <c r="M10" t="n">
-        <v>32.9538820138243</v>
+        <v>32.88496048770335</v>
       </c>
       <c r="N10" t="n">
-        <v>1531.603094876764</v>
+        <v>1527.845196455004</v>
       </c>
       <c r="O10" t="n">
-        <v>39.135701027026</v>
+        <v>39.08766041163124</v>
       </c>
       <c r="P10" t="n">
-        <v>297.5300743924865</v>
+        <v>297.5485037525368</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21190,7 +21239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K404"/>
+  <dimension ref="A1:K405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44221,6 +44270,63 @@
         </is>
       </c>
     </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>-42.21794758673304,173.86442204735042</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>-42.21799306138327,173.86351354651495</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>-42.21815533789328,173.86281105626367</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>-42.218398384204434,173.86218841966857</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>-42.21866809686944,173.86148153199736</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>-42.218982172203326,173.86077529683612</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>-42.219496224530495,173.86018075192905</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>-42.2199276676374,173.85963368368348</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>-42.22035011131512,173.85908407678227</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
